--- a/TASK2/Scenariji/SC01_RegistracijaNovogClana.xlsx
+++ b/TASK2/Scenariji/SC01_RegistracijaNovogClana.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Registracija novog clana</t>
+          <t>Registracija novog člana</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Administrator registruje novog clana teretane unosenjem svih potrebnih podataka. Sistem automatski generira QR kod.</t>
+          <t>Administrator registruje novog člana teretane unosenjem svih potrebnih podataka. Sistem automatski generiše QR kod.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Registracija novih clanova sa svim potrebnim podacima; Generisanje QR koda za svakog registrovanog clana</t>
+          <t>Registracija novih članova sa svim potrebnim podacima; Generisanje QR koda za svakog registrovanog člana</t>
         </is>
       </c>
     </row>
@@ -504,24 +504,24 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Novi clan je registrovan, QR kod je generiran i dodijeljen clanu.</t>
+          <t>Novi član je registrovan, QR kod je generiran i dodijeljen članu.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Registracija nije izvrsena zbog nevalidnih podataka ili duplikata email-a.</t>
+          <t>Registracija nije izvršena zbog nevalidnih podataka ili duplikata email-a.</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Administrator unosi podatke clana, sistem validira i kreira profil sa QR kodom.</t>
+          <t>Administrator unosi podatke člana, sistem validira i kreira profil sa QR kodom.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Nevalidni podaci, Email vec postoji</t>
-        </is>
-      </c>
-    </row>
+          <t>Nevalidni podaci, Email već postoji</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -595,14 +596,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1. Pokretanje opcije za registraciju novog clana</t>
+          <t>1. Pokretanje opcije za registraciju novog člana</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2. Prikaz forme za unos podataka clana</t>
+          <t>2. Prikaz forme za unos podataka člana</t>
         </is>
       </c>
     </row>
@@ -630,14 +631,14 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6. Kreiranje profila clana sa datumom registracije</t>
+          <t>6. Kreiranje profila člana sa datumom registracije</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>7. Automatsko generisanje jedinstvenog QR koda</t>
+          <t>7. Automatsko Generisanje jedinstvenog QR koda</t>
         </is>
       </c>
     </row>
@@ -648,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
@@ -695,10 +697,11 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Email vec postoji</t>
+          <t>Alternativni Tok - Email već postoji</t>
         </is>
       </c>
     </row>
@@ -717,21 +720,21 @@
     <row r="32">
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>5a. Sistem detektuje da email vec postoji u bazi</t>
+          <t>5a. Sistem detektuje da email već postoji u bazi</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>5b. Prikaz poruke da clan sa tim email-om vec postoji</t>
+          <t>5b. Prikaz poruke da član sa tim email-om već postoji</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>5c. Administrator unosi drugi email ili pronalazi postojeceg clana</t>
+          <t>5c. Administrator unosi drugi email ili pronalazi postojećeg člana</t>
         </is>
       </c>
     </row>
